--- a/sheets/대금율보/검수/다향.xlsx
+++ b/sheets/대금율보/검수/다향.xlsx
@@ -5078,7 +5078,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹
+          <t xml:space="preserve">湳
 㴌</t>
         </is>
       </c>
@@ -5092,7 +5092,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹
+          <t xml:space="preserve">湳
 㴌</t>
         </is>
       </c>
@@ -5174,7 +5174,7 @@
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 姑太</t>
         </is>
       </c>
@@ -5202,14 +5202,14 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌‹
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐‹
+          <t xml:space="preserve">㶐
 㴌</t>
         </is>
       </c>
@@ -5218,7 +5218,7 @@
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 汰</t>
         </is>
       </c>
@@ -5271,7 +5271,7 @@
       <c r="E6" s="24"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 姑林</t>
         </is>
       </c>
@@ -5292,14 +5292,14 @@
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 太黃</t>
         </is>
       </c>
       <c r="M6" s="24"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰潢</t>
         </is>
       </c>
@@ -5327,7 +5327,7 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐‹
+          <t xml:space="preserve">㶐
 湳</t>
         </is>
       </c>
@@ -5341,7 +5341,7 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌‹
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
@@ -5369,7 +5369,7 @@
       <c r="O7" s="22"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南‹
+          <t xml:space="preserve">南
 㴌</t>
         </is>
       </c>
@@ -5528,7 +5528,7 @@
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㑲姑</t>
         </is>
       </c>
@@ -5572,7 +5572,7 @@
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹
+          <t xml:space="preserve">湳
 㴌</t>
         </is>
       </c>
@@ -5585,7 +5585,7 @@
       <c r="G11" s="22"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
@@ -5699,7 +5699,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐‹
+          <t xml:space="preserve">㶐
 㴌</t>
         </is>
       </c>
@@ -5712,7 +5712,7 @@
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㶐‹
+          <t xml:space="preserve">㶐
 林</t>
         </is>
       </c>
@@ -5738,7 +5738,7 @@
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 淋</t>
         </is>
       </c>
@@ -5752,7 +5752,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢汰</t>
         </is>
       </c>
@@ -5766,7 +5766,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋ʒ</t>
         </is>
       </c>
@@ -5780,14 +5780,14 @@
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢汰</t>
         </is>
       </c>
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 黃太</t>
         </is>
       </c>
@@ -5815,7 +5815,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌‹
+          <t xml:space="preserve">㴌
 淋</t>
         </is>
       </c>
@@ -5823,7 +5823,7 @@
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋‹</t>
+淋</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -5841,14 +5841,14 @@
       <c r="I15" s="22"/>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌‹
+          <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
       <c r="K15" s="22"/>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑‹
+          <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
@@ -5859,7 +5859,7 @@
       <c r="Q15" s="22"/>
       <c r="R15" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢?
+          <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
@@ -5983,7 +5983,7 @@
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋‹</t>
+淋</t>
         </is>
       </c>
       <c r="K18" s="24"/>

--- a/sheets/대금율보/검수/다향.xlsx
+++ b/sheets/대금율보/검수/다향.xlsx
@@ -5016,32 +5016,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="114.74" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
       <c r="T3" s="21"/>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="114.74" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="114.74" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="114.74" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="114.74" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="114.74" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="114.74" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="114.74" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="114.74" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="114.74" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="114.74" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="114.74" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="114.74" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="114.74" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="114.74" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="114.74" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6024,6 +6024,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>